--- a/Reference/LHparams_2023assessment.xlsx
+++ b/Reference/LHparams_2023assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\openMSE\NPSWO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A91C1900-36BC-4900-ACAB-8483A25B2BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D999F280-EE25-40E8-BD4D-E0EEAAB6724A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0586FA9B-9293-4891-8766-4A362A345880}"/>
+    <workbookView xWindow="420" yWindow="0" windowWidth="10920" windowHeight="12168" xr2:uid="{0586FA9B-9293-4891-8766-4A362A345880}"/>
   </bookViews>
   <sheets>
     <sheet name="2023 Assessment Report" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Parameter</t>
   </si>
@@ -50,42 +50,10 @@
     <t>M</t>
   </si>
   <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="MathJax_Main"/>
-      </rPr>
-      <t>∞</t>
-    </r>
-  </si>
-  <si>
-    <t>von Bertalanffy asymptotic length</t>
-  </si>
-  <si>
     <t>K</t>
   </si>
   <si>
     <t>growth coefficient</t>
-  </si>
-  <si>
-    <r>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="MathJax_Main"/>
-      </rPr>
-      <t>0</t>
-    </r>
-  </si>
-  <si>
-    <t>expected age at L=0</t>
   </si>
   <si>
     <t>a</t>
@@ -116,22 +84,6 @@
     <t>Length corresponding with 50% probability of maturity</t>
   </si>
   <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="MathJax_Main"/>
-      </rPr>
-      <t>95</t>
-    </r>
-  </si>
-  <si>
-    <t>Length corresponding with 95% probability of maturity</t>
-  </si>
-  <si>
     <t>h</t>
   </si>
   <si>
@@ -177,12 +129,58 @@
   <si>
     <t>Brodziak 2020</t>
   </si>
+  <si>
+    <t>Brodziak, J. (2020). On the probably distribution of stock-recruitment steepness for Western and Central North Pacific swordfish. ISC/20/BILLWG-01/06.</t>
+  </si>
+  <si>
+    <t>DeMartini, E.E., Uchiyama, J.H., Humphreys Jr., R.L., Sampaga, J.D. and Williams, H.A. (2007). Age and growth of swordfish (Xiphias gladius) caught by the Hawaii-based pelagic longline fishery. Fish. Bull. 105:356-367.</t>
+  </si>
+  <si>
+    <t>Kapur, M., Brodziak, J. Fletcher, E. and Yau, A. (2017). Summary of Life History and Stock Assessment Results for Pacific Blue Marlin, Western and Central North Pacific Striped Marlin, and North Pacific Swordfish. ISC/17/BILLWG-01/02.</t>
+  </si>
+  <si>
+    <t>Assumed</t>
+  </si>
+  <si>
+    <r>
+      <t>L @ A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MathJax_Math-italic"/>
+      </rPr>
+      <t>min</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>L @ A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MathJax_Math-italic"/>
+      </rPr>
+      <t>max</t>
+    </r>
+  </si>
+  <si>
+    <t>Length at maximum age (EFL)</t>
+  </si>
+  <si>
+    <t>Length at minimum age (EFL)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,6 +213,12 @@
     </font>
     <font>
       <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="MathJax_Math-italic"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="MathJax_Math-italic"/>
     </font>
@@ -611,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95324917-057B-45F7-8C4C-57B9256FB505}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="17.21875"/>
@@ -627,10 +631,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -641,69 +645,75 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.200000000000003" thickBot="1">
+      <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="27" thickBot="1">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="D3" s="3">
+        <v>83.2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="40.200000000000003" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3">
         <v>226.3</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D4" s="3">
         <v>206.4</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="27" thickBot="1">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.246</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.27100000000000002</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27" thickBot="1">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.246</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="53.4" thickBot="1">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4">
         <v>1.2999999999999999E-5</v>
@@ -712,15 +722,15 @@
         <v>1.2999999999999999E-5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="40.200000000000003" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3">
         <v>3.07</v>
@@ -729,64 +739,71 @@
         <v>3.07</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="66.599999999999994" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3">
         <v>143.68</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="66.599999999999994" thickBot="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27" thickBot="1">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" ht="27" thickBot="1">
+      <c r="D9" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="66">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
-        <v>0.9</v>
+        <v>0.42</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="66">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
-        <v>0.42</v>
-      </c>
-      <c r="E11" s="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>